--- a/Ahmedabad-May-2025.xlsx
+++ b/Ahmedabad-May-2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="73">
   <si>
     <t>Sr. No</t>
   </si>
@@ -94,6 +94,9 @@
     <t>Profit %</t>
   </si>
   <si>
+    <t>Unnamed: 26</t>
+  </si>
+  <si>
     <t>Ahmedabad</t>
   </si>
   <si>
@@ -172,7 +175,7 @@
     <t>AMAZE</t>
   </si>
   <si>
-    <t>Crysta</t>
+    <t>CRYSTA</t>
   </si>
   <si>
     <t>CITROEN</t>
@@ -190,13 +193,55 @@
     <t>INVICTO</t>
   </si>
   <si>
-    <t>-</t>
+    <t>15/05/2025</t>
+  </si>
+  <si>
+    <t>14/08/2017</t>
+  </si>
+  <si>
+    <t>29/05/2018</t>
+  </si>
+  <si>
+    <t>28/02/2019</t>
+  </si>
+  <si>
+    <t>30/03/2019</t>
+  </si>
+  <si>
+    <t>26/04/2019</t>
+  </si>
+  <si>
+    <t>29/03/2022</t>
+  </si>
+  <si>
+    <t>18/07/2022</t>
+  </si>
+  <si>
+    <t>17/10/2023</t>
+  </si>
+  <si>
+    <t>27/02/2025</t>
+  </si>
+  <si>
+    <t>26/07/2024</t>
+  </si>
+  <si>
+    <t>30/09/2021</t>
+  </si>
+  <si>
+    <t>21/04/2025</t>
+  </si>
+  <si>
+    <t>16/08/2024</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <sz val="11"/>
@@ -249,11 +294,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -548,10 +594,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z24"/>
+  <dimension ref="A1:AA24"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:26">
+    <row r="1" spans="1:27">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -630,28 +676,31 @@
       <c r="Z1" s="1" t="s">
         <v>25</v>
       </c>
+      <c r="AA1" s="1" t="s">
+        <v>26</v>
+      </c>
     </row>
-    <row r="2" spans="1:26">
+    <row r="2" spans="1:27">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D2">
         <v>2025</v>
       </c>
       <c r="E2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F2" t="s">
-        <v>51</v>
-      </c>
-      <c r="G2">
-        <v>45792</v>
+        <v>52</v>
+      </c>
+      <c r="G2" t="s">
+        <v>59</v>
       </c>
       <c r="H2">
         <v>29</v>
@@ -711,27 +760,27 @@
         <v>33.31</v>
       </c>
     </row>
-    <row r="3" spans="1:26">
+    <row r="3" spans="1:27">
       <c r="A3">
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D3">
         <v>2025</v>
       </c>
       <c r="E3" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F3" t="s">
-        <v>51</v>
-      </c>
-      <c r="G3">
-        <v>45792</v>
+        <v>52</v>
+      </c>
+      <c r="G3" t="s">
+        <v>59</v>
       </c>
       <c r="H3">
         <v>29</v>
@@ -791,27 +840,27 @@
         <v>35.49</v>
       </c>
     </row>
-    <row r="4" spans="1:26">
+    <row r="4" spans="1:27">
       <c r="A4">
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D4">
         <v>2025</v>
       </c>
       <c r="E4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F4" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G4" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="H4">
         <v>312282</v>
@@ -871,27 +920,27 @@
         <v>35.17</v>
       </c>
     </row>
-    <row r="5" spans="1:26">
+    <row r="5" spans="1:27">
       <c r="A5">
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D5">
         <v>2025</v>
       </c>
       <c r="E5" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F5" t="s">
-        <v>52</v>
-      </c>
-      <c r="G5" t="s">
-        <v>58</v>
+        <v>53</v>
+      </c>
+      <c r="G5" s="2">
+        <v>43283</v>
       </c>
       <c r="H5">
         <v>301225</v>
@@ -951,27 +1000,27 @@
         <v>25.89</v>
       </c>
     </row>
-    <row r="6" spans="1:26">
+    <row r="6" spans="1:27">
       <c r="A6">
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C6" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D6">
         <v>2025</v>
       </c>
       <c r="E6" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F6" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G6" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="H6">
         <v>195393</v>
@@ -1031,27 +1080,27 @@
         <v>-5.47</v>
       </c>
     </row>
-    <row r="7" spans="1:26">
+    <row r="7" spans="1:27">
       <c r="A7">
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C7" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D7">
         <v>2025</v>
       </c>
       <c r="E7" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F7" t="s">
-        <v>52</v>
-      </c>
-      <c r="G7" t="s">
-        <v>58</v>
+        <v>53</v>
+      </c>
+      <c r="G7" s="2">
+        <v>43350</v>
       </c>
       <c r="H7">
         <v>284117</v>
@@ -1111,27 +1160,27 @@
         <v>48.08</v>
       </c>
     </row>
-    <row r="8" spans="1:26">
+    <row r="8" spans="1:27">
       <c r="A8">
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C8" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D8">
         <v>2025</v>
       </c>
       <c r="E8" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F8" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G8" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="H8">
         <v>336050</v>
@@ -1191,27 +1240,27 @@
         <v>55.91</v>
       </c>
     </row>
-    <row r="9" spans="1:26">
+    <row r="9" spans="1:27">
       <c r="A9">
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C9" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D9">
         <v>2025</v>
       </c>
       <c r="E9" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F9" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G9" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="H9">
         <v>347004</v>
@@ -1271,27 +1320,27 @@
         <v>56.18</v>
       </c>
     </row>
-    <row r="10" spans="1:26">
+    <row r="10" spans="1:27">
       <c r="A10">
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C10" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D10">
         <v>2025</v>
       </c>
       <c r="E10" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F10" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G10" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="H10">
         <v>314980</v>
@@ -1351,27 +1400,27 @@
         <v>47.65</v>
       </c>
     </row>
-    <row r="11" spans="1:26">
+    <row r="11" spans="1:27">
       <c r="A11">
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C11" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D11">
         <v>2025</v>
       </c>
       <c r="E11" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F11" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G11" t="s">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="H11">
         <v>345665</v>
@@ -1431,27 +1480,27 @@
         <v>48.86</v>
       </c>
     </row>
-    <row r="12" spans="1:26">
+    <row r="12" spans="1:27">
       <c r="A12">
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C12" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D12">
         <v>2025</v>
       </c>
       <c r="E12" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F12" t="s">
-        <v>52</v>
-      </c>
-      <c r="G12">
-        <v>43899</v>
+        <v>53</v>
+      </c>
+      <c r="G12" s="2">
+        <v>44077</v>
       </c>
       <c r="H12">
         <v>145104</v>
@@ -1511,27 +1560,27 @@
         <v>78.88</v>
       </c>
     </row>
-    <row r="13" spans="1:26">
+    <row r="13" spans="1:27">
       <c r="A13">
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C13" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D13">
         <v>2025</v>
       </c>
       <c r="E13" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F13" t="s">
-        <v>52</v>
-      </c>
-      <c r="G13">
-        <v>44470</v>
+        <v>53</v>
+      </c>
+      <c r="G13" s="2">
+        <v>44206</v>
       </c>
       <c r="H13">
         <v>92664</v>
@@ -1591,27 +1640,27 @@
         <v>40.49</v>
       </c>
     </row>
-    <row r="14" spans="1:26">
+    <row r="14" spans="1:27">
       <c r="A14">
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C14" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D14">
         <v>2025</v>
       </c>
       <c r="E14" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F14" t="s">
-        <v>52</v>
-      </c>
-      <c r="G14">
-        <v>44649</v>
+        <v>53</v>
+      </c>
+      <c r="G14" t="s">
+        <v>65</v>
       </c>
       <c r="H14">
         <v>104979</v>
@@ -1671,27 +1720,27 @@
         <v>16.68</v>
       </c>
     </row>
-    <row r="15" spans="1:26">
+    <row r="15" spans="1:27">
       <c r="A15">
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C15" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D15">
         <v>2025</v>
       </c>
       <c r="E15" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F15" t="s">
-        <v>52</v>
-      </c>
-      <c r="G15">
-        <v>44760</v>
+        <v>53</v>
+      </c>
+      <c r="G15" t="s">
+        <v>66</v>
       </c>
       <c r="H15">
         <v>61878</v>
@@ -1751,27 +1800,27 @@
         <v>4.85</v>
       </c>
     </row>
-    <row r="16" spans="1:26">
+    <row r="16" spans="1:27">
       <c r="A16">
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C16" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D16">
         <v>2025</v>
       </c>
       <c r="E16" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F16" t="s">
-        <v>52</v>
-      </c>
-      <c r="G16">
-        <v>45216</v>
+        <v>53</v>
+      </c>
+      <c r="G16" t="s">
+        <v>67</v>
       </c>
       <c r="H16">
         <v>119300</v>
@@ -1836,22 +1885,22 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C17" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D17">
         <v>2025</v>
       </c>
       <c r="E17" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F17" t="s">
-        <v>52</v>
-      </c>
-      <c r="G17">
-        <v>45715</v>
+        <v>53</v>
+      </c>
+      <c r="G17" t="s">
+        <v>68</v>
       </c>
       <c r="H17">
         <v>13155</v>
@@ -1916,22 +1965,22 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C18" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D18">
         <v>2025</v>
       </c>
       <c r="E18" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F18" t="s">
-        <v>53</v>
-      </c>
-      <c r="G18">
-        <v>45499</v>
+        <v>54</v>
+      </c>
+      <c r="G18" t="s">
+        <v>69</v>
       </c>
       <c r="H18">
         <v>20762</v>
@@ -1996,22 +2045,22 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C19" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D19">
         <v>2025</v>
       </c>
       <c r="E19" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F19" t="s">
-        <v>53</v>
-      </c>
-      <c r="G19">
-        <v>45499</v>
+        <v>54</v>
+      </c>
+      <c r="G19" t="s">
+        <v>69</v>
       </c>
       <c r="H19">
         <v>17695</v>
@@ -2076,22 +2125,22 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C20" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D20">
         <v>2025</v>
       </c>
       <c r="E20" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F20" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G20" t="s">
-        <v>58</v>
+        <v>70</v>
       </c>
       <c r="H20">
         <v>319625</v>
@@ -2156,22 +2205,22 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C21" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D21">
         <v>2025</v>
       </c>
       <c r="E21" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F21" t="s">
-        <v>55</v>
-      </c>
-      <c r="G21">
-        <v>44987</v>
+        <v>56</v>
+      </c>
+      <c r="G21" s="2">
+        <v>44960</v>
       </c>
       <c r="H21">
         <v>66213</v>
@@ -2236,22 +2285,22 @@
         <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C22" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D22">
         <v>2025</v>
       </c>
       <c r="E22" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F22" t="s">
-        <v>56</v>
-      </c>
-      <c r="G22">
-        <v>45768</v>
+        <v>57</v>
+      </c>
+      <c r="G22" t="s">
+        <v>71</v>
       </c>
       <c r="H22">
         <v>650</v>
@@ -2316,22 +2365,22 @@
         <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C23" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D23">
         <v>2025</v>
       </c>
       <c r="E23" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F23" t="s">
-        <v>56</v>
-      </c>
-      <c r="G23">
-        <v>45768</v>
+        <v>57</v>
+      </c>
+      <c r="G23" t="s">
+        <v>71</v>
       </c>
       <c r="H23">
         <v>823</v>
@@ -2396,22 +2445,22 @@
         <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C24" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D24">
         <v>2025</v>
       </c>
       <c r="E24" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F24" t="s">
-        <v>57</v>
-      </c>
-      <c r="G24">
-        <v>45520</v>
+        <v>58</v>
+      </c>
+      <c r="G24" t="s">
+        <v>72</v>
       </c>
       <c r="H24">
         <v>45903</v>
